--- a/experiment_results/combined_sweep/rtt_bursts_S3_atk10pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S3_atk10pct_wu500000.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>697053</t>
+          <t>406184</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>824947</t>
+          <t>418769</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>880230</t>
+          <t>461467</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>998396</t>
+          <t>536935</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1114172</t>
+          <t>577243</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1213386</t>
+          <t>636149</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1376422</t>
+          <t>740278</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1553283</t>
+          <t>813010</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1735906</t>
+          <t>922901</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1930980</t>
+          <t>1008085</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2119191</t>
+          <t>1111113</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2275152</t>
+          <t>1164046</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2492716</t>
+          <t>1328676</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2675361</t>
+          <t>1346691</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2688278</t>
+          <t>1341593</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2683185</t>
+          <t>1341598</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
